--- a/PUCSL_Submission_Response_Workbook.xlsx
+++ b/PUCSL_Submission_Response_Workbook.xlsx
@@ -338,7 +338,7 @@
     <t>Abatis/Platinum company profile &amp; credentials pack</t>
   </si>
   <si>
-    <t>20+ yrs CNI protection; first client Swiss government/military; zero reported breaches, zero CVEs; deployments incl. Gulf smart-city OT programmes</t>
+    <t>20+ yrs CNI protection; first client Swiss government/military; zero reported breaches, zero registered vulnerabilities; deployments incl. Gulf smart-city OT programmes</t>
   </si>
   <si>
     <t>Platinum/Abatis financial statements (if required of both JV partners)</t>
@@ -1070,7 +1070,7 @@
     <t>Technical partner track record?</t>
   </si>
   <si>
-    <t>Abatis: Swiss company incorporated Oct 2004; first client was the Swiss government — technology designed at the request of the Swiss government and implemented by the Swiss military for CNI protection. In 20+ years: zero reported breaches against the code and zero CVEs registered — both believed unique in the industry.</t>
+    <t>Abatis: Swiss company incorporated Oct 2004; first client was the Swiss government — technology designed at the request of the Swiss government and implemented by the Swiss military for CNI protection. In 20+ years: zero reported breaches against the code and zero publicly registered security vulnerabilities — both believed unique in the industry.</t>
   </si>
   <si>
     <t>What differentiates the technical approach?</t>

--- a/PUCSL_Submission_Response_Workbook.xlsx
+++ b/PUCSL_Submission_Response_Workbook.xlsx
@@ -17,12 +17,14 @@
     <sheet name="Submission Checklist" sheetId="2" r:id="rId2"/>
     <sheet name="Technical Response Matrix" sheetId="3" r:id="rId3"/>
     <sheet name="Approach &amp; Methodology" sheetId="4" r:id="rId4"/>
-    <sheet name="Work Plan (16 wks)" sheetId="5" r:id="rId5"/>
+    <sheet name="Old Plan (superseded)" sheetId="5" r:id="rId5"/>
     <sheet name="Staffing &amp; Rates" sheetId="6" r:id="rId6"/>
     <sheet name="Financial Summary" sheetId="7" r:id="rId7"/>
     <sheet name="Key Personnel" sheetId="8" r:id="rId8"/>
     <sheet name="Q&amp;A Answers" sheetId="9" r:id="rId9"/>
     <sheet name="Outstanding Items" sheetId="10" r:id="rId10"/>
+    <sheet name="TECH-7 Staffing Schedule" sheetId="11" r:id="rIdT7"/>
+    <sheet name="TECH-8 Gantt (25 wks)" sheetId="12" r:id="rIdT8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -275,10 +277,10 @@
     <t>Bid Security / Bid Declaration (if required)</t>
   </si>
   <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>Ask EML — not visible in draft RFP discussion</t>
+    <t>NOT REQUIRED</t>
+  </si>
+  <si>
+    <t>NOT REQUIRED — no bid security requirement in the RFP Data Sheet; SC-6 advance-payment guarantee is post-award</t>
   </si>
   <si>
     <t>D</t>
@@ -875,10 +877,10 @@
     <t>Proposal Management &amp; Coordination</t>
   </si>
   <si>
-    <t>Subtotal — Abatis (120 man-days + lump sums)</t>
-  </si>
-  <si>
-    <t>Subtotal — EML (145 man-days + lump sums)</t>
+    <t>Subtotal — Abatis (200 man-days + lump sums)</t>
+  </si>
+  <si>
+    <t>Subtotal — EML (220 man-days + lump sums)</t>
   </si>
   <si>
     <t>Section</t>
@@ -914,16 +916,16 @@
     <t>Base Cost</t>
   </si>
   <si>
-    <t>Profit @ 15%</t>
+    <t>Profit @ 30% of base cost</t>
   </si>
   <si>
     <t>Total (excl. taxes)</t>
   </si>
   <si>
-    <t>VAT @ 18%</t>
-  </si>
-  <si>
-    <t>SSCL @ 2.5%</t>
+    <t>VAT @ 18% — confirm applicability (would add USD 62,577.45; currently excluded from grand total)</t>
+  </si>
+  <si>
+    <t>SSCL @ 2.5% (formula corrected — was calculated at 2.0%)</t>
   </si>
   <si>
     <t>GRAND TOTAL (USD, incl. VAT + SSCL)</t>
@@ -932,7 +934,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1. Mirrors Budget_cyber_security.xlsx (agreed internal pricing, 29 Jul 2026).</t>
+    <t>1. All pricing in USD (Platinum prices in USD; EML reprices local components into LKR — RFP ITC 3.8, p. ITC-6). Evaluation converts foreign currency to LKR at selling exchange rate (ITC 5.6).</t>
   </si>
   <si>
     <t>2. Original internal sizing was ~USD 350k; EML flagged price sensitivity — current pricing reflects competitive positioning with 80/20 technical/price evaluation.</t>
@@ -941,7 +943,7 @@
     <t>3. Confirm with EML: whether financial proposal must be in USD or LKR; tax treatment of the foreign JV partner (VAT/SSCL applicability to offshore services).</t>
   </si>
   <si>
-    <t>4. Value split ≈ 69% Abatis / 31% EML of professional fees — consistent with agreed ~70/30 allocation.</t>
+    <t>4. Value split now ≈ 82% Abatis / 18% EML of professional fees — DIVERGES from the ~70/30 basis agreed with EML (27–28 Jul emails). Confirm with Jeewaka before FIN forms are shared.</t>
   </si>
   <si>
     <t>Role in Assignment</t>
@@ -1127,7 +1129,7 @@
     <t>EML / Jeewaka</t>
   </si>
   <si>
-    <t>Master requirement list — this workbook's response matrix must be verified against it clause-by-clause</t>
+    <t>RESOLVED 29 Jul — official RFP received; full gap analysis issued (PUCSL_RFP_Gap_Analysis docs, refs to RFP pages)</t>
   </si>
   <si>
     <t>Confirmation whether additional forms exist (compliance spreadsheet / Excel annexes)</t>
@@ -1139,7 +1141,7 @@
     <t>Exact submission deadline time, place &amp; number of copies (hard/soft)</t>
   </si>
   <si>
-    <t>Deadline believed Thu 30 Jul; submission is physical in Sri Lanka via EML</t>
+    <t>RESOLVED — 30 Jul 2026, 2:00 pm SLST, PUCSL 6th Fl, BOC Merchant Tower, No. 28 St. Michael's Rd, Colombo 3. Original + 2 copies of both proposals + USB (Technical only); envelope markings per ITC 4.4 (pp. DATA-2–3)</t>
   </si>
   <si>
     <t>Bid security requirement (amount, form, validity)</t>
@@ -1148,7 +1150,7 @@
     <t>EML / tender doc</t>
   </si>
   <si>
-    <t>Unknown — could be a hard blocker if bank guarantee needed</t>
+    <t>RESOLVED — NO bid security required (nothing in Data Sheet); SC-6 advance-payment guarantee applies post-award only</t>
   </si>
   <si>
     <t>Signed JV Letter of Intent (Platinum Malta lead)</t>
@@ -1979,6 +1981,1881 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORM TECH-7 — STAFFING SCHEDULE (RFP p. Forms-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme: 25 weeks ≈ 6 months (M6 = weeks 21–25). O = office input, F = field input (man-days). 1 staff-month = 21 working days. Names to be inserted from signed CVs (one candidate per position).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Position</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Party</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total man-days</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff-months</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[insert name]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team Leader</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign — Abatis</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[insert name]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior OT/ICS Cybersecurity Specialist</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign — Abatis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[insert name]</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cybersecurity Governance Specialist</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign — Abatis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
+      </c>
+      <c r="M9">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[insert name]</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEC 62443 / C2M2 Specialist</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign — Abatis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>20</v>
+      </c>
+      <c r="M10">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[insert name]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Training &amp; Capacity Building Specialist</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign — Abatis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+      <c r="K11">
+        <v>6</v>
+      </c>
+      <c r="L11">
+        <v>20</v>
+      </c>
+      <c r="M11">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal — Foreign (Abatis)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O+F</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>22</v>
+      </c>
+      <c r="G12">
+        <v>45</v>
+      </c>
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>47</v>
+      </c>
+      <c r="J12">
+        <v>32</v>
+      </c>
+      <c r="K12">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>200</v>
+      </c>
+      <c r="M12">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power Systems / SCADA Engineer (DPM)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>12</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <v>60</v>
+      </c>
+      <c r="M13">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14">
+        <v>8</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>40</v>
+      </c>
+      <c r="M14">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local Electrical Engineer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
+      </c>
+      <c r="M15">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>30</v>
+      </c>
+      <c r="M16">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stakeholder Engagement Specialist</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>15</v>
+      </c>
+      <c r="M17">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QA/QC Manager</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical Report Coordinator</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>15</v>
+      </c>
+      <c r="M19">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[EML nominee]</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Administrator</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">National — EML</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
+        <v>30</v>
+      </c>
+      <c r="M20">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Subtotal — National (EML)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O+F</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
+        <v>48</v>
+      </c>
+      <c r="H21">
+        <v>44</v>
+      </c>
+      <c r="I21">
+        <v>50</v>
+      </c>
+      <c r="J21">
+        <v>41</v>
+      </c>
+      <c r="K21">
+        <v>19</v>
+      </c>
+      <c r="L21">
+        <v>220</v>
+      </c>
+      <c r="M21">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>40</v>
+      </c>
+      <c r="G22">
+        <v>93</v>
+      </c>
+      <c r="H22">
+        <v>74</v>
+      </c>
+      <c r="I22">
+        <v>97</v>
+      </c>
+      <c r="J22">
+        <v>73</v>
+      </c>
+      <c r="K22">
+        <v>43</v>
+      </c>
+      <c r="L22">
+        <v>420</v>
+      </c>
+      <c r="M22">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field input reflects two international missions (M2 and M4; ≈20 Abatis site-days) plus EML's continuous local field programme (70 field days).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOTE — pricing decision pending (gap S5): RFP expected man-days for scored positions are TL 30 / Specialist 60 / SCADA 50 (pp. DATA-3–4); table shows current agreed loading.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="62" customWidth="1"/>
+    <col min="2" max="2" width="4.2" customWidth="1"/>
+    <col min="3" max="3" width="4.2" customWidth="1"/>
+    <col min="4" max="4" width="4.2" customWidth="1"/>
+    <col min="5" max="5" width="4.2" customWidth="1"/>
+    <col min="6" max="6" width="4.2" customWidth="1"/>
+    <col min="7" max="7" width="4.2" customWidth="1"/>
+    <col min="8" max="8" width="4.2" customWidth="1"/>
+    <col min="9" max="9" width="4.2" customWidth="1"/>
+    <col min="10" max="10" width="4.2" customWidth="1"/>
+    <col min="11" max="11" width="4.2" customWidth="1"/>
+    <col min="12" max="12" width="4.2" customWidth="1"/>
+    <col min="13" max="13" width="4.2" customWidth="1"/>
+    <col min="14" max="14" width="4.2" customWidth="1"/>
+    <col min="15" max="15" width="4.2" customWidth="1"/>
+    <col min="16" max="16" width="4.2" customWidth="1"/>
+    <col min="17" max="17" width="4.2" customWidth="1"/>
+    <col min="18" max="18" width="4.2" customWidth="1"/>
+    <col min="19" max="19" width="4.2" customWidth="1"/>
+    <col min="20" max="20" width="4.2" customWidth="1"/>
+    <col min="21" max="21" width="4.2" customWidth="1"/>
+    <col min="22" max="22" width="4.2" customWidth="1"/>
+    <col min="23" max="23" width="4.2" customWidth="1"/>
+    <col min="24" max="24" width="4.2" customWidth="1"/>
+    <col min="25" max="25" width="4.2" customWidth="1"/>
+    <col min="26" max="26" width="4.2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FORM TECH-8 — WORK SCHEDULE / 25-WEEK GANTT (RFP p. Forms-11; deliverables &amp; payments per TOR §6–7, pp. GC-7–GC-9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█ = activity in progress   ◆ = contract deliverable (payment milestone)   ▲ = workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activity / Deliverable</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W11</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W12</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W13</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W14</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W16</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W18</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W19</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W20</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W21</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W22</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W23</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mobilisation, NDA execution, kick-off</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Methodology confirmation &amp; data-request register</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1 — INCEPTION REPORT (10% payment)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information gathering &amp; document review</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site mission 1 (NSCC + 2 facilities)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-level interviews</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2 — INTERIM PROGRESS REPORT (20%)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Site mission 2 (remaining facilities)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 C2M2 Maturity Assessment Report (10 domains, MIL scoring)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2 Technical Vulnerability &amp; Gap Analysis Report (SCADA/EMS, DNP3/IEC 61850)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 International Standards Alignment Matrix (ISO 27001, IEC 62443, NIST CSF)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Verified Evidence Ledger (continuous compilation)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 Maturity Profile &amp; Executive Dashboard</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D3 — DATA ASSESSMENT &amp; PRELIMINARY FINDINGS REPORT (20%)</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Cybersecurity Remediation Roadmap (prioritised, cost-aware)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 Cybersecurity Policy &amp; Standards Manual (target MILs)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2 Audit Program &amp; RACI Matrix (checklists, audit cycle)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.3 Performance Metrics &amp; Re-assessment Protocol (KPIs)</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workshop — Technical Findings &amp; Governance Framework</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PILOT VALIDATION of Audit Framework on selected systems (TOR §e)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Framework refinement from pilot; TNO internal-audit guidelines &amp; tools</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1 Operational Toolkit Package (risk registers, IR templates, dashboards)</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 Standard Operating Procedures (SOPs)</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.3 Regulatory Compliance Sustainability Guide</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workshop — Knowledge Transfer (auditor enablement)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D4 — DRAFT FINAL REPORT (30%)</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Client review &amp; incorporation of comments</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 Knowledge Transfer &amp; Training Report</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">█</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workshop — Executive Presentation &amp; Final</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D5 — FINAL REPORT &amp; close-out (20%)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◆</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment milestones per TOR §6 (pp. GC-7–GC-8): D1 W4 = 10%; D2 W8 = 20%; D3 W16 = 20%; D4 W22 = 30%; D5 W25 = 20%. Duration 25 weeks per TOR §7 (p. GC-9).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E29"/>
@@ -3750,8 +5627,8 @@
         <v>293</v>
       </c>
       <c r="C12" s="4">
-        <f>C10*0.02</f>
-        <v>6953.05</v>
+        <f>C10*0.025</f>
+        <v>8691.3125</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -3761,7 +5638,7 @@
       </c>
       <c r="C13" s="5">
         <f>C10+C12</f>
-        <v>354605.55</v>
+        <v>356343.8125</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="12.75" x14ac:dyDescent="0.2"/>
